--- a/index.xlsx
+++ b/index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Progetti\ntJobsAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Progetti\GitHub\ntJobsAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F827A3D-B18D-4078-971E-F3B22712AD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9CCD5-94A6-4090-B97C-8DDA088393DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="files" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="114">
   <si>
     <t>NAME</t>
   </si>
@@ -210,9 +210,6 @@
     <t>Prompt generazione ntJobsApp (Open)</t>
   </si>
   <si>
-    <t xml:space="preserve">aiobsOS.py      </t>
-  </si>
-  <si>
     <t>ntj_admin.py</t>
   </si>
   <si>
@@ -288,9 +285,6 @@
     <t>aiSysTimestamp.py</t>
   </si>
   <si>
-    <t xml:space="preserve"> ncDictToString.py</t>
-  </si>
-  <si>
     <t>ncMailSimple.py</t>
   </si>
   <si>
@@ -333,10 +327,49 @@
     <t>Classe principale acJobsOS</t>
   </si>
   <si>
-    <t xml:space="preserve">aiobsJobsJobs.py      </t>
-  </si>
-  <si>
-    <t>SubClasse JobsOS.Jobs</t>
+    <t>aiSysDictToString.py</t>
+  </si>
+  <si>
+    <t>acJobsJobs.py</t>
+  </si>
+  <si>
+    <t>acJobsMail.py</t>
+  </si>
+  <si>
+    <t>acJobsStart.py</t>
+  </si>
+  <si>
+    <t>acJobsUsers.py</t>
+  </si>
+  <si>
+    <t>Test for aiJobsOS</t>
+  </si>
+  <si>
+    <t>JobsOS Users</t>
+  </si>
+  <si>
+    <t>JobsOS Jobs</t>
+  </si>
+  <si>
+    <t>JobsOS Mailing</t>
+  </si>
+  <si>
+    <t>JobsOS Start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aiJobsOS.py      </t>
+  </si>
+  <si>
+    <t>SYS.OS</t>
+  </si>
+  <si>
+    <t>SYS.APP</t>
+  </si>
+  <si>
+    <t>APP.NTJ</t>
+  </si>
+  <si>
+    <t>SYS.SYS</t>
   </si>
 </sst>
 </file>
@@ -418,7 +451,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -736,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1048508"/>
+  <dimension ref="A1:K1048506"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" style="1" customWidth="1"/>
@@ -789,7 +822,7 @@
     </row>
     <row r="2" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>11</v>
@@ -807,7 +840,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>3</v>
@@ -820,52 +853,49 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C3" s="6">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="9">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="6"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="9">
         <v>46029</v>
       </c>
-      <c r="J3" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6"/>
-      <c r="I4" s="9"/>
+      <c r="J4" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
@@ -876,8 +906,11 @@
       <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I5" s="9">
         <v>46029</v>
@@ -888,25 +921,25 @@
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3">
-        <v>10</v>
+        <v>24</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>3</v>
@@ -920,16 +953,16 @@
     </row>
     <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="C7" s="6">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>22</v>
@@ -938,13 +971,13 @@
         <v>13</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I7" s="9">
-        <v>46029</v>
+        <v>46059</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>14</v>
@@ -952,13 +985,13 @@
     </row>
     <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="C8" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>2</v>
@@ -970,24 +1003,22 @@
         <v>13</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="9">
-        <v>46059</v>
-      </c>
+      <c r="I8" s="9"/>
       <c r="J8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -996,13 +1027,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>13</v>
+        <v>112</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -1014,40 +1045,42 @@
     </row>
     <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="9"/>
+      <c r="I10" s="9">
+        <v>46047</v>
+      </c>
       <c r="J10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -1062,7 +1095,7 @@
         <v>13</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>3</v>
@@ -1079,7 +1112,7 @@
         <v>81</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -1094,7 +1127,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -1108,10 +1141,10 @@
     </row>
     <row r="13" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6">
         <v>1</v>
@@ -1126,7 +1159,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>3</v>
@@ -1140,10 +1173,10 @@
     </row>
     <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C14" s="6">
         <v>1</v>
@@ -1158,7 +1191,7 @@
         <v>13</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1172,10 +1205,10 @@
     </row>
     <row r="15" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C15" s="6">
         <v>1</v>
@@ -1190,7 +1223,7 @@
         <v>13</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -1207,7 +1240,7 @@
         <v>85</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16" s="6">
         <v>1</v>
@@ -1222,7 +1255,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>3</v>
@@ -1236,10 +1269,10 @@
     </row>
     <row r="17" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="C17" s="6">
         <v>1</v>
@@ -1254,7 +1287,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1268,10 +1301,10 @@
     </row>
     <row r="18" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C18" s="6">
         <v>1</v>
@@ -1280,77 +1313,77 @@
         <v>25</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I18" s="9">
-        <v>46047</v>
+        <v>46031</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>80</v>
+      <c r="A19" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>59</v>
       </c>
       <c r="C19" s="6">
         <v>1</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="15" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I19" s="9">
-        <v>46031</v>
+        <v>46029</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>59</v>
+      <c r="A20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="C20" s="6">
         <v>1</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I20" s="9">
         <v>46029</v>
@@ -1370,10 +1403,10 @@
         <v>1</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>13</v>
@@ -1391,21 +1424,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="6">
-        <v>1</v>
+      <c r="B22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="3">
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>13</v>
@@ -1414,7 +1447,7 @@
         <v>13</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I22" s="9">
         <v>46029</v>
@@ -1425,19 +1458,19 @@
     </row>
     <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C23" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>13</v>
@@ -1457,19 +1490,19 @@
     </row>
     <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C24" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>13</v>
@@ -1489,19 +1522,19 @@
     </row>
     <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3">
         <v>10</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>13</v>
@@ -1513,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="I25" s="9">
-        <v>46029</v>
+        <v>46059</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>14</v>
@@ -1521,19 +1554,19 @@
     </row>
     <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C26" s="3">
         <v>10</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>13</v>
@@ -1545,7 +1578,7 @@
         <v>3</v>
       </c>
       <c r="I26" s="9">
-        <v>46059</v>
+        <v>46029</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>14</v>
@@ -1553,10 +1586,10 @@
     </row>
     <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C27" s="3">
         <v>10</v>
@@ -1565,7 +1598,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>13</v>
@@ -1574,7 +1607,7 @@
         <v>13</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I27" s="9">
         <v>46029</v>
@@ -1585,7 +1618,7 @@
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>77</v>
@@ -1615,21 +1648,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="3">
-        <v>10</v>
+        <v>93</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="6">
+        <v>1</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>13</v>
@@ -1638,10 +1671,10 @@
         <v>13</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I29" s="9">
-        <v>46029</v>
+        <v>46065</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>14</v>
@@ -1649,38 +1682,166 @@
     </row>
     <row r="30" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I30" s="9">
-        <v>46059</v>
+        <v>46065</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="1048507" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048508" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="9">
+        <v>46065</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="9">
+        <v>46065</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="6">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="9">
+        <v>46065</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="9">
+        <v>46065</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1048505" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048506" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/index.xlsx
+++ b/index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Progetti\ntJobsAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B590B0A9-9EAB-409C-A2A9-F452F35E1F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F827A3D-B18D-4078-971E-F3B22712AD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="files" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="103">
   <si>
     <t>NAME</t>
   </si>
@@ -232,6 +232,111 @@
   </si>
   <si>
     <t>Mirror per GITHUB: Kit aiJobs</t>
+  </si>
+  <si>
+    <t>ntjobs_config.ini</t>
+  </si>
+  <si>
+    <t>Inbox</t>
+  </si>
+  <si>
+    <t>APP.CMD</t>
+  </si>
+  <si>
+    <t>Config Dati per NTJOBSOS</t>
+  </si>
+  <si>
+    <t>ntjobs_groups.csv</t>
+  </si>
+  <si>
+    <t>ntjobs_users.csv</t>
+  </si>
+  <si>
+    <t>ntjobs_actions.csv</t>
+  </si>
+  <si>
+    <t>DATI</t>
+  </si>
+  <si>
+    <t>Archive</t>
+  </si>
+  <si>
+    <t>Folder dove arrivano i jobs.ini e files degli utenti</t>
+  </si>
+  <si>
+    <t>Jobs Archiviati</t>
+  </si>
+  <si>
+    <t>aiJobsTest.py</t>
+  </si>
+  <si>
+    <t>Funzioni e Classi di supporto a ntJobsOS che si appoggiano a jData per  funzioni di Test</t>
+  </si>
+  <si>
+    <t>aiSysBase.py</t>
+  </si>
+  <si>
+    <t>aiSysFileio.py</t>
+  </si>
+  <si>
+    <t>aiSysConfig.py</t>
+  </si>
+  <si>
+    <t>aiSysStrings.py</t>
+  </si>
+  <si>
+    <t>aiSysTimestamp.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ncDictToString.py</t>
+  </si>
+  <si>
+    <t>ncMailSimple.py</t>
+  </si>
+  <si>
+    <t>Classe invio mail SMPT</t>
+  </si>
+  <si>
+    <t>Da Dizionario a Stringa json, xml</t>
+  </si>
+  <si>
+    <t>Gestione Timestamp</t>
+  </si>
+  <si>
+    <t>Gestione Dizionario Config</t>
+  </si>
+  <si>
+    <t>Stringhe</t>
+  </si>
+  <si>
+    <t>File Io</t>
+  </si>
+  <si>
+    <t>Dizionari e funzioni base</t>
+  </si>
+  <si>
+    <t>admin_pytest.cmd</t>
+  </si>
+  <si>
+    <t>Esecuione test</t>
+  </si>
+  <si>
+    <t>ntjobs_billing.csv</t>
+  </si>
+  <si>
+    <t>Biling file di esecuzione jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acJobsOS.py   </t>
+  </si>
+  <si>
+    <t>Classe principale acJobsOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aiobsJobsJobs.py      </t>
+  </si>
+  <si>
+    <t>SubClasse JobsOS.Jobs</t>
   </si>
 </sst>
 </file>
@@ -292,7 +397,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,6 +416,12 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -324,7 +435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -335,14 +446,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -359,6 +464,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -620,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1048496"/>
+  <dimension ref="A1:K1048508"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" style="1" customWidth="1"/>
@@ -637,48 +753,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -696,7 +812,7 @@
       <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="9">
         <v>46029</v>
       </c>
       <c r="J2" s="5" t="s">
@@ -704,28 +820,31 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="A3" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="6">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="11">
+        <v>3</v>
+      </c>
+      <c r="I3" s="9">
         <v>46029</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -733,63 +852,34 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="3">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="11">
-        <v>46029</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="6"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7">
-        <v>2</v>
+        <v>56</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="11">
+        <v>17</v>
+      </c>
+      <c r="I5" s="9">
         <v>46029</v>
       </c>
       <c r="J5" s="5" t="s">
@@ -798,46 +888,48 @@
     </row>
     <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3">
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="11"/>
+      <c r="I6" s="9">
+        <v>46029</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="6">
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>22</v>
@@ -851,20 +943,22 @@
       <c r="H7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I7" s="11"/>
+      <c r="I7" s="9">
+        <v>46029</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>2</v>
@@ -881,28 +975,28 @@
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I8" s="11">
-        <v>46029</v>
+      <c r="I8" s="9">
+        <v>46059</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>25</v>
+      <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>13</v>
@@ -913,28 +1007,26 @@
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="11">
-        <v>46029</v>
-      </c>
+      <c r="I9" s="9"/>
       <c r="J9" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="7">
+        <v>63</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="6">
         <v>1</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>13</v>
@@ -943,23 +1035,21 @@
         <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="11">
-        <v>46029</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="I10" s="9"/>
       <c r="J10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="7">
+        <v>54</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="6">
         <v>1</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -975,17 +1065,622 @@
         <v>13</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="6">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="9">
+        <v>46047</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="9">
+        <v>46031</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I21" s="9">
         <v>46029</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="1048495" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="1048496" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J21" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="3">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="3">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="3">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="9">
+        <v>46059</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="3">
+        <v>10</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="3">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="3">
+        <v>10</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="9">
+        <v>46029</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="9">
+        <v>46059</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1048507" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048508" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1011,18 +1706,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="11">
         <v>45474</v>
       </c>
       <c r="B2" t="s">
@@ -1033,7 +1728,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="12">
         <v>45507</v>
       </c>
       <c r="B3" t="s">
@@ -1044,7 +1739,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="11">
         <v>45611</v>
       </c>
       <c r="B4" t="s">
@@ -1072,16 +1767,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>34</v>
       </c>
     </row>
